--- a/branches/chore/docs-cleanup/StructureDefinition-example-patient.xlsx
+++ b/branches/chore/docs-cleanup/StructureDefinition-example-patient.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T20:17:19+00:00</t>
+    <t>2026-08-05T20:43:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
